--- a/results/climate_change_breakdown/2050/propanol production, fossil_GLO.xlsx
+++ b/results/climate_change_breakdown/2050/propanol production, fossil_GLO.xlsx
@@ -417,7 +417,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>3.233106995893993</v>
+        <v>3.233106995893996</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -434,7 +434,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>3.233106995893993</v>
+        <v>3.233106995893996</v>
       </c>
       <c r="E3">
         <v>1</v>
